--- a/fileNaming/자산정리/하단사건번호_하면또는구분수정_df는일단하면으로수정함.xlsx
+++ b/fileNaming/자산정리/하단사건번호_하면또는구분수정_df는일단하면으로수정함.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,7 +601,7 @@
       <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -699,22 +699,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20411429</t>
+          <t>20427504</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>n1005876</t>
+          <t>n1028235</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>n1005876김문정</t>
+          <t>n1028235서동호</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21457383</t>
+          <t>21458874</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>김문정</t>
+          <t>서동호</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>창원지방법원</t>
+          <t>대구회생법원</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026하면2035</t>
+          <t>2026하면275</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr"/>
@@ -763,7 +763,7 @@
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -773,29 +773,29 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2026하단2035</t>
+          <t>2026하단275</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20454559</t>
+          <t>20411429</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>n1030037</t>
+          <t>n1005876</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>n1030037전영철</t>
+          <t>n1005876김문정</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21457499</t>
+          <t>21457383</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>전영철</t>
+          <t>김문정</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>의정부지방법원</t>
+          <t>창원지방법원</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026하면20066</t>
+          <t>2026하면2035</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -830,13 +830,13 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>채권1 주식회사 솔림헬프자산관리대부</t>
+          <t>채권자 주식회사 솔림헬프자산관리대부</t>
         </is>
       </c>
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr"/>
@@ -844,7 +844,7 @@
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -854,39 +854,39 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2026하단20066</t>
+          <t>2026하단2035</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>20413694</t>
+          <t>20454559</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>n1055682</t>
+          <t>n1030037</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>n1055682이재규</t>
+          <t>n1030037전영철</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21457445</t>
+          <t>21457499</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>보증인</t>
+          <t>채무자</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>이재규</t>
+          <t>전영철</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>서울회생법원</t>
+          <t>의정부지방법원</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2025하면10623</t>
+          <t>2026하면20066</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -911,13 +911,13 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>채권자 주식회사 솔림헬프자산관리대부</t>
+          <t>채권1 주식회사 솔림헬프자산관리대부</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
@@ -925,39 +925,39 @@
       <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>보증인</t>
+          <t>채무자</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2025하단10623</t>
+          <t>2026하단20066</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>20424139</t>
+          <t>20426020</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>n1022624</t>
+          <t>n1024602</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>n1022624조현덕</t>
+          <t>n1024602김은경</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21457174</t>
+          <t>21458875</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>조현덕</t>
+          <t>김은경</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>인천지방법원</t>
+          <t>대구회생법원</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2025하면102641</t>
+          <t>2026하면10822</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -992,23 +992,19 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>채권2. 주식회사 솔림헬프자산관리대부</t>
+          <t>채권자 주식회사 솔림헬프자산과리대부</t>
         </is>
       </c>
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="2" t="inlineStr">
         <is>
           <t>채무자</t>
@@ -1016,86 +1012,406 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2025하단102641</t>
+          <t>2026하단10822</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>20421295</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>n1055178</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>n1055178김해순</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21458873</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>보증인</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>김해순</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>파산</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>대구회생법원</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026하면10052</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>채권 주식회사 솔림헬프자산관리대부</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>보증인</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2026하단10052</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>20514818</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>n1050124</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>n1050124조한기</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>21458876</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>채무자</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>조한기</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>파산</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>인천지방법원</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2026하면100018</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>채권7 주식회사 솔림헬프자산관리대부</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>채무자</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2026하단100018</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>20413694</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>n1055682</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>n1055682이재규</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21457445</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>보증인</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>이재규</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>파산</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>서울회생법원</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2025하면10623</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>채권자 주식회사 솔림헬프자산관리대부</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>보증인</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2025하단10623</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>20424139</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>n1022624</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>n1022624조현덕</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21457174</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>채무자</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>조현덕</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>파산</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>인천지방법원</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2025하면102641</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>채권2. 주식회사 솔림헬프자산관리대부</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>채무자</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>2025하단102641</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>20453429</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>n1033016</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>n1033016노형준</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>21457552</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>채무자</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>채무자</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>노형준</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>파산</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>부산회생법원</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>2025하면101686</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>포함</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>채권3. 주식회사 솔림헬프자산관리대부</t>
         </is>
       </c>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t>채무자</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>채무자</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
         <is>
           <t>2025하단101686</t>
         </is>
